--- a/uctalent_jobs.xlsx
+++ b/uctalent_jobs.xlsx
@@ -704,12 +704,8 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Hi [FirstName],
-I came across your profile and was impressed by your background. We're helping a client fill a Fraud &amp; Risk Specialist/Leader role based in Hanoi, Vietnam (₫30,000,000-₫35,000,000/monthly), and your experience seems like a strong match.
-The role focuses on: Human Resource (HR), Software and IT Services, Team Management.
-Would you be open to a quick chat to explore this opportunity?
-Best regards,
-Nhat - UCTalent</t>
+          <t>Hi [Name], impressed by your risk management and data analysis background. I'm recruiting a Fraud &amp; Risk Specialist/Leader in Hanoi (₫30-35M/month) for a client — strong fit for your KYC, SQL, and leadership experience. Open to a brief chat?
+Best regards</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr"/>
@@ -727,7 +723,7 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>ready_to_connect</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
@@ -2494,7 +2490,7 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/stevendu,https://www.linkedin.com/in/aloysius-ekezie-65419224b,https://www.linkedin.com/in/amen-stoney-214452230,https://www.linkedin.com/in/dmitriy-polumiskov,https://www.linkedin.com/in/alexei-rusu-dev,https://linkedin.com/in/nicholas-ericksen-993b66ab,https://www.linkedin.com/in/moelh,https://www.linkedin.com/in/joel-francis-541821305,https://www.linkedin.com/in/timambler,https://www.linkedin.com/in/crystalcardona,https://www.linkedin.com/in/adeel-bukhari-4521635,https://www.linkedin.com/in/ameinalmoughrabi,https://www.linkedin.com/in/daniel-ho7,https://www.linkedin.com/in/chrisjagius,https://www.linkedin.com/in/ilan-rouson-b8aa5562,https://www.linkedin.com/in/contreras9,https://www.linkedin.com/in/mohammed-bensassi,https://www.linkedin.com/in/mohamed-elmahy</t>
+          <t>https://www.linkedin.com/in/stevendu,https://www.linkedin.com/in/aloysius-ekezie-65419224b,https://www.linkedin.com/in/amen-stoney-214452230,https://www.linkedin.com/in/dmitriy-polumiskov,https://www.linkedin.com/in/alexei-rusu-dev,https://linkedin.com/in/nicholas-ericksen-993b66ab,https://www.linkedin.com/in/moelh,https://www.linkedin.com/in/joel-francis-541821305,https://www.linkedin.com/in/timambler,https://www.linkedin.com/in/crystalcardona,https://www.linkedin.com/in/adeel-bukhari-4521635,https://www.linkedin.com/in/ameinalmoughrabi,https://www.linkedin.com/in/daniel-ho7,https://www.linkedin.com/in/chrisjagius,https://www.linkedin.com/in/ilan-rouson-b8aa5562,https://www.linkedin.com/in/contreras9,https://www.linkedin.com/in/mohammed-bensassi,https://www.linkedin.com/in/mohamed-elmahy,https://www.linkedin.com/in/anton-james-ja,https://www.linkedin.com/in/navdeepkumar2025,https://www.linkedin.com/in/oswaldo-almazo</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2536,7 +2532,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>https://uctalent.io/referral/BirthdayN/truVABkpOttB6r2_Fm7J4?utm_source=headhunter&amp;utm_medium=referral</t>
+          <t>https://uctalent.io/referral/BirthdayN/qYg0VbSBL3DcpYkSBXeQK?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2586,12 +2582,8 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Hi [FirstName],
-I came across your profile and was impressed by your experience. We're currently hiring for a Software Engineer role based in New York, United States ($150,000-$215,000/annually), and your background seems like a great match.
-Key skills we're looking for: Engineering, Software and IT Services, Node.js.
-Would you be open to a quick chat to explore this opportunity?
-Best regards,
-Nhat - UCTalent</t>
+          <t>Hi — your background in Node.js, React, and AWS infrastructure caught my attention. I'm representing a client in New York hiring a Software Engineer ($150K–$215K) with your stack. Worth a quick chat if you're open to it?
+Best regards</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2660,7 +2652,11 @@
 https://uctalent.io/referral/BirthdayN/truVABkpOttB6r2Fm7J4?utmsource=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
-      <c r="U16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stevendu,https://www.linkedin.com/in/aloysius-ekezie-65419224b,https://www.linkedin.com/in/amen-stoney-214452230,https://www.linkedin.com/in/dmitriy-polumiskov,https://www.linkedin.com/in/alexei-rusu-dev,https://linkedin.com/in/nicholas-ericksen-993b66ab,https://www.linkedin.com/in/moelh,https://www.linkedin.com/in/joel-francis-541821305,https://www.linkedin.com/in/timambler,https://www.linkedin.com/in/crystalcardona,https://www.linkedin.com/in/anton-james-ja,https://www.linkedin.com/in/adeel-bukhari-4521635,https://www.linkedin.com/in/ameinalmoughrabi,https://www.linkedin.com/in/daniel-ho7,https://www.linkedin.com/in/chrisjagius,https://www.linkedin.com/in/ilan-rouson-b8aa5562,https://www.linkedin.com/in/mohammed-bensassi,https://www.linkedin.com/in/contreras9,https://www.linkedin.com/in/navdeepkumar2025,https://www.linkedin.com/in/oswaldo-almazo</t>
+        </is>
+      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
           <t>pending</t>
@@ -2668,7 +2664,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>searching</t>
+          <t>ready_to_connect</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">

--- a/uctalent_jobs.xlsx
+++ b/uctalent_jobs.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>https://uctalent.io/referral/Nhat_Nguyen_Sinh453954/MTkFDprgo7kUvDAjmY1AD?utm_source=headhunter&amp;utm_medium=referral</t>
+          <t>https://uctalent.io/referral/BirthdayN/T97FRCiR3Zv4FTp9X83nx?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -714,41 +714,39 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Hi [Name], your strong background in Java and Spring Boot caught my eye. I'm headhunting for a Full-stack Engineer in HCMC with a salary of $3,000-$3,300. I believe your skills would be a great fit for my client. Open to a brief chat? Best regards.</t>
+          <t>Hi [Name], your strong background in Java and Spring Boot caught my eye. I’m headhunting for a Full-stack Engineer role in HCMC ($3,000–$3,300) for a client. I think you'd be a great fit—would you be open to a quick chat about the details?
+Best regards,</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>A great product is only as strong as the engineering foundation behind it.
-I am currently looking for a Full-Stack Software Engineer to join a high-performing team in Ho Chi Minh City. This role is central to building and scaling robust Corporate Services platforms where technical precision is the priority. 📍
-We are looking for an engineer who is comfortable navigating the complexities of Java and Spring Boot while maintaining a disciplined workflow with Git. This isn't just about shipping features; it’s about contributing to an engineering culture that values clean code and scalable architecture. 🔧
-If you are a developer who prefers direct communication and high-impact work over corporate red tape, this opportunity is for you. Stop worrying about being ghosted and get your profile seen by the right people.
+          <t>High-growth products don't just need coders; they need engineers who understand the "why" behind the architecture.
+I am currently headhunting for a Full-stack Software Engineer based in Ho Chi Minh City. This role is central to a team delivering Corporate Services, where stability and scalability are the top priorities. 📍
+If your toolkit includes Java and Spring Boot, and you have mastered the discipline of Git-based workflows, I would like to chat. We are looking for someone who values clean Engineering over quick fixes. 🔧
+The market is crowded, but roles with this level of technical ownership are rare. Stop being ghosted by generic portals and apply where your technical depth is actually recognized.
 Details and application link in comments. 👇
-#UCTalent #FullstackDeveloper #HCMCJobs</t>
+#FullstackDeveloper #Java #UCTalent</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>HCMC devs: Stop sending CVs into the void. 📍
-Hiring a Full-stack Software Engineer for a Corporate Services team in HCMC. Need Java, Spring Boot, and Git expertise. 🔧 High-impact work, clear growth.
+          <t>Engineering high-scale corporate systems in HCMC.
+Looking for a Full-stack Engineer skilled in Java, Spring Boot, and Git. Join a team focused on solid architecture and real-world impact. No fluff, just pure engineering. 📍
+Link in comments
+#UCTalent #HCMC #JavaJobs</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>Great code is only half the battle; the real challenge is building systems that scale with business needs. 🚀
+We’re looking for a Full-stack Software Engineer in HCMC to join a Corporate Services team. If you’re proficient in Java, Spring Boot, and Git, this is an opportunity to solve complex engineering problems in a high-impact environment.
 Link in comments 👇
-#UCTalent #HCMCJobs #JavaDev</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>Most developers have the skills but lack the right bridge to the opportunity. 🌉
-I’m looking for a Full-Stack Software Engineer in HCMC. If you’re strong with Java, Spring Boot, and Git, this role in Corporate Services is a chance to build impactful systems without the usual hiring noise. 🔧
-Stop being ghosted. Let’s get your profile seen by the right people.
-Link in comments 👇
-#SoftwareEngineer #HCMC #UCTalent</t>
+#Java #Fullstack #HCMCJobs</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>HIRING: FULL-STACK SOFTWARE ENGINEER
-Stop being ghosted by job apps.
-AI matches you directly to hiring managers.
 📍 Ho Chi Minh City, Vietnam
 💰 $3,000-$3,300/monthly
 Apply via Nhat - UCTalent
@@ -758,19 +756,19 @@
       <c r="R2" s="3" t="inlineStr">
         <is>
           <t>Apply directly via our AI Agent — no middlemen, no ghosting:
-https://uctalent.io/referral/NhatNguyenSinh453954/MTkFDprgo7kUvDAjmY1AD?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/T97FRCiR3Zv4FTp9X83nx?utmsource=headhunter&amp;utmmedium=referral</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
           <t>Apply directly via our AI Agent:
-https://uctalent.io/referral/NhatNguyenSinh453954/MTkFDprgo7kUvDAjmY1AD?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/T97FRCiR3Zv4FTp9X83nx?utmsource=headhunter&amp;utmmedium=referral</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
           <t>Apply ngay để AI Agent giúp bạn kết nối trực tiếp với hiring manager:
-https://uctalent.io/referral/NhatNguyenSinh453954/MTkFDprgo7kUvDAjmY1AD?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/T97FRCiR3Zv4FTp9X83nx?utmsource=headhunter&amp;utmmedium=referral</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -1017,7 +1015,11 @@
           <t>Data QA ENGINEER</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utm_source=headhunter&amp;utm_medium=referral</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>320</t>
@@ -1073,13 +1075,70 @@
 Nhat - UCTalent</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr"/>
-      <c r="O5" s="7" t="inlineStr"/>
-      <c r="P5" s="7" t="inlineStr"/>
-      <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
-      <c r="S5" s="7" t="inlineStr"/>
-      <c r="T5" s="7" t="inlineStr"/>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>Most QA Engineers are just glorified manual testers waiting for a bug to pop up. If you're tired of mindless clicking and want to actually own the integrity of a massive data pipeline, listen up.
+The market is flooded with "QA experts" who can't tell a table from a spreadsheet. We don't need that. We need a Data QA Engineer who knows that data integrity is the backbone of any serious business.
+My client in Vietnam is looking for someone who doesn't just "test"—they engineer quality.
+The Reality:
+- You’ll be deep in Azure and Databricks, ensuring the Data Warehouse doesn't turn into a data swamp.
+- This is Corporate Services on a high level. Accuracy isn't a "nice to have"; it’s the only thing that matters.
+- Forget basic UI testing. We need high-level QAQC skills that actually impact the bottom line.
+Why bother?
+- Stop wasting your talent on basic web apps.
+- Work with a stack that actually challenges your brain.
+- Fast-paced, no-BS environment.
+I’ve been ghosted before, and I know it sucks. That’s why I do things differently at UCTalent. You apply, you get an answer. Simple.
+If you’re a pro and tired of the noise, let’s move. ⚡
+Link in comments 👇
+#UCTalent #DataEngineering #QAQC #VietnamJobs</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>Most Data Engineers ship garbage. Stop pretending "good enough" works. 🔥
+Need a Data QA in VN who actually cares about precision. Azure + Databricks + DWH. Stop playing safe and start breaking things. ⚡
+Link in comments 👇
+#UCTalent #DataQA</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>Most "Data-driven" companies are flying blind because their pipelines are trash. 🗑️
+Stop letting bad data ruin decisions. If you’re a Data QA pro who breathes Azure and Databricks, I have a client in VN who actually values your brain. No more ghosting, just real impact.
+Link in comments 👇
+#UCTalent #DataEngineering</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>HIRING: Data QA ENGINEER
+Stop being ghosted by job apps.
+AI matches you directly to hiring managers.
+📍 Vietnam
+💰 ₫30,000,000-₫40,000,000/monthly
+Apply via Nhat - UCTalent
+uctalent.io</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>Apply directly via our AI Agent:
+https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utmsource=headhunter&amp;utmmedium=referral</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>Apply directly:
+https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utmsource=headhunter&amp;utmmedium=referral</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>Apply ngay:
+https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utmsource=headhunter&amp;utmmedium=referral</t>
+        </is>
+      </c>
       <c r="U5" s="7" t="inlineStr"/>
       <c r="V5" s="6" t="inlineStr">
         <is>

--- a/uctalent_jobs.xlsx
+++ b/uctalent_jobs.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>https://uctalent.io/referral/BirthdayN/T97FRCiR3Zv4FTp9X83nx?utm_source=headhunter&amp;utm_medium=referral</t>
+          <t>https://uctalent.io/referral/BirthdayN/Viqx5HGBqZB6_fktQpzG1?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -714,39 +714,46 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Hi [Name], your strong background in Java and Spring Boot caught my eye. I’m headhunting for a Full-stack Engineer role in HCMC ($3,000–$3,300) for a client. I think you'd be a great fit—would you be open to a quick chat about the details?
-Best regards,</t>
+          <t>Hi [Name], I was impressed by your track record with Java and Spring Boot. I’m headhunting for a Full-stack Engineer in HCMC ($3,000-$3,300). Given your experience, I think you'd be a great fit. Open to a brief chat to share more?
+Best regards</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>High-growth products don't just need coders; they need engineers who understand the "why" behind the architecture.
-I am currently headhunting for a Full-stack Software Engineer based in Ho Chi Minh City. This role is central to a team delivering Corporate Services, where stability and scalability are the top priorities. 📍
-If your toolkit includes Java and Spring Boot, and you have mastered the discipline of Git-based workflows, I would like to chat. We are looking for someone who values clean Engineering over quick fixes. 🔧
-The market is crowded, but roles with this level of technical ownership are rare. Stop being ghosted by generic portals and apply where your technical depth is actually recognized.
-Details and application link in comments. 👇
-#FullstackDeveloper #Java #UCTalent</t>
+          <t>I remember how it felt to refresh my inbox for days, hoping for just one human response instead of another automated rejection. It’s tough out there right now, and honestly, being a dev is about more than just closing tickets—it’s about finding a team that actually values your craft and your time. 💛
+I’m currently helping a client in Ho Chi Minh City find a Full-stack Software Engineer who wants to do more than just "write code." If you’re someone who loves the reliability of Java and Spring Boot but also enjoys the challenge of building meaningful Corporate Services, this might be the right spot for you.
+We’re looking for someone who:
+✨ Knows their way around Git and collaborative Engineering practices.
+✨ Enjoys solving complex problems that actually impact business operations.
+✨ Wants to grow in a supportive environment where your voice is heard.
+I’ve been in your shoes, and I know how much it sucks to be ghosted. That’s why I’m making sure every applicant through UCTalent gets the clarity they deserve. No corporate fluff, just a real opportunity to level up with a team that cares. 🙌
+If you're ready for a change and want to work with a team that respects your talent, I’d love to see your profile. 🤝
+Link in comments! 👋
+#UCTalent #Web3Jobs #DecentralizedHiring</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>Engineering high-scale corporate systems in HCMC.
-Looking for a Full-stack Engineer skilled in Java, Spring Boot, and Git. Join a team focused on solid architecture and real-world impact. No fluff, just pure engineering. 📍
-Link in comments
-#UCTalent #HCMC #JavaJobs</t>
+          <t>I know how it feels to send a CV and hear nothing but silence. 💛
+HCMC: Looking for a Full-Stack dev (Java/Spring Boot) for a Corporate Services role. I'll handle the gatekeepers for you. 🤝
+Link in comments ✨
+#UCTalent #JavaJobs</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Great code is only half the battle; the real challenge is building systems that scale with business needs. 🚀
-We’re looking for a Full-stack Software Engineer in HCMC to join a Corporate Services team. If you’re proficient in Java, Spring Boot, and Git, this is an opportunity to solve complex engineering problems in a high-impact environment.
+          <t>I know that feeling of refreshing your inbox, hoping for one "real" reply. The market is noisy right now, and it’s easy to feel like just another CV in a pile. 💛
+If you’re a Java/Spring Boot dev in HCMC, I’ve got a role with a client that actually values the person behind the code. You’ll be working on Corporate Services, using your Git skills to build things that matter.
+Let’s get you out of the "ghosting" cycle. 🙌
 Link in comments 👇
-#Java #Fullstack #HCMCJobs</t>
+#UCTalent #HCMCJobs #JavaDev</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>HIRING: FULL-STACK SOFTWARE ENGINEER
+Stop being ghosted by job apps.
+AI matches you directly to hiring managers.
 📍 Ho Chi Minh City, Vietnam
 💰 $3,000-$3,300/monthly
 Apply via Nhat - UCTalent
@@ -755,20 +762,20 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>Apply directly via our AI Agent — no middlemen, no ghosting:
-https://uctalent.io/referral/BirthdayN/T97FRCiR3Zv4FTp9X83nx?utmsource=headhunter&amp;utmmedium=referral</t>
+          <t>Apply directly via our AI Agent:
+https://uctalent.io/referral/BirthdayN/Viqx5HGBqZB6fktQpzG1?utmsource=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
           <t>Apply directly via our AI Agent:
-https://uctalent.io/referral/BirthdayN/T97FRCiR3Zv4FTp9X83nx?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/Viqx5HGBqZB6fktQpzG1?utmsource=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
           <t>Apply ngay để AI Agent giúp bạn kết nối trực tiếp với hiring manager:
-https://uctalent.io/referral/BirthdayN/T97FRCiR3Zv4FTp9X83nx?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/Viqx5HGBqZB6fktQpzG1?utmsource=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -783,7 +790,7 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>ready_to_connect</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
@@ -1139,7 +1146,11 @@
 https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utmsource=headhunter&amp;utmmedium=referral</t>
         </is>
       </c>
-      <c r="U5" s="7" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/danhhoa,https://linkedin.com/in/ng%C3%B4-th%E1%BB%8Bnh-1066431b6,https://linkedin.com/in/uyen-truong-thu,https://linkedin.com/in/hieuhoangvan1802,https://linkedin.com/in/pankaj-negi-a3b95113a,https://linkedin.com/in/linhnguyentrankhanh,https://www.linkedin.com/in/tiennguyenducmanh,https://linkedin.com/in/hungngvan,https://linkedin.com/in/linh-le-nhat-9575991b8,https://linkedin.com/in/th%E1%BB%8Bnh-nguy%E1%BB%85n-c%C3%B4ng-a455a9318,https://linkedin.com/in/l%C3%AA-thanh-tu%E1%BA%A5n-1707171aa,https://linkedin.com/in/hoang-nam-le-eminent,https://linkedin.com/in/ngolinhcbg,https://linkedin.com/in/truong-thu-thao-57a42b221,https://linkedin.com/in/kieu-trinh-341454130,https://linkedin.com/in/dung-pham-b86590272,https://linkedin.com/in/kushal-shrestha-4329691a0,https://linkedin.com/in/lia-rahmi-adriani-279079b9,https://linkedin.com/in/marius-secu-26ab8011b,https://linkedin.com/in/andraachim</t>
+        </is>
+      </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
           <t>pending</t>
@@ -1147,7 +1158,7 @@
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>ready_to_connect</t>
         </is>
       </c>
       <c r="X5" s="6" t="inlineStr">

--- a/uctalent_jobs.xlsx
+++ b/uctalent_jobs.xlsx
@@ -763,19 +763,19 @@
       <c r="R2" s="3" t="inlineStr">
         <is>
           <t>Apply directly via our AI Agent:
-https://uctalent.io/referral/BirthdayN/Viqx5HGBqZB6fktQpzG1?utmsource=headhunter&amp;utm_medium=referral</t>
+https://uctalent.io/referral/BirthdayN/Viqx5HGBqZB6fktQpzG1?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
           <t>Apply directly via our AI Agent:
-https://uctalent.io/referral/BirthdayN/Viqx5HGBqZB6fktQpzG1?utmsource=headhunter&amp;utm_medium=referral</t>
+https://uctalent.io/referral/BirthdayN/Viqx5HGBqZB6fktQpzG1?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
           <t>Apply ngay để AI Agent giúp bạn kết nối trực tiếp với hiring manager:
-https://uctalent.io/referral/BirthdayN/Viqx5HGBqZB6fktQpzG1?utmsource=headhunter&amp;utm_medium=referral</t>
+https://uctalent.io/referral/BirthdayN/Viqx5HGBqZB6fktQpzG1?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utm_source=headhunter&amp;utm_medium=referral</t>
+          <t>https://uctalent.io/referral/quick_process/BN84zMIfAiuLk1OvpDqnr?utm_source=copy_link&amp;utm_medium=job_referral&amp;utm_campaign=job_referral&amp;utm_content=recruiter</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1075,10 +1075,8 @@
       <c r="M5" s="7" t="inlineStr">
         <is>
           <t>Hi [FirstName],
-I came across your profile and was impressed by your background. We're helping a client fill a Data QA ENGINEER role based in Vietnam (₫30,000,000-₫40,000,000/monthly), and your experience seems like a strong match.
-The role focuses on: QAQC, Corporate Services, Azure.
-Would you be open to a quick chat to explore this opportunity?
-Best regards,
+Data QA ENGINEER — based in Vietnam (₫30,000,000-₫40,000,000/monthly). Your skills (QAQC, Corporate Services, Azure) fit.
+Open to a quick chat?
 Nhat - UCTalent</t>
         </is>
       </c>
@@ -1131,19 +1129,19 @@
       <c r="R5" s="7" t="inlineStr">
         <is>
           <t>Apply directly via our AI Agent:
-https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
           <t>Apply directly:
-https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
           <t>Apply ngay:
-https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="U5" s="7" t="inlineStr">
@@ -1696,19 +1694,19 @@
       <c r="R10" s="5" t="inlineStr">
         <is>
           <t>Apply directly via our AI Agent:
-https://uctalent.io/referral/BirthdayN/2eHqmbDAoLg9Sy-cXyvuQ?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/2eHqmbDAoLg9Sy-cXyvuQ?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
           <t>Apply directly via our AI Agent:
-https://uctalent.io/referral/BirthdayN/2eHqmbDAoLg9Sy-cXyvuQ?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/2eHqmbDAoLg9Sy-cXyvuQ?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="T10" s="5" t="inlineStr">
         <is>
           <t>Apply ngay:
-https://uctalent.io/referral/BirthdayN/2eHqmbDAoLg9Sy-cXyvuQ?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/2eHqmbDAoLg9Sy-cXyvuQ?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="U10" s="5" t="inlineStr"/>
@@ -2448,19 +2446,19 @@
       <c r="R17" s="5" t="inlineStr">
         <is>
           <t>Apply directly via our AI Agent:
-https://uctalent.io/referral/BirthdayN/yVVs9S3K-94JyZtoYOUuC?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/yVVs9S3K-94JyZtoYOUuC?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
           <t>Apply directly via our AI Agent:
-https://uctalent.io/referral/BirthdayN/yVVs9S3K-94JyZtoYOUuC?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/yVVs9S3K-94JyZtoYOUuC?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="T17" s="5" t="inlineStr">
         <is>
           <t>Apply ngay để AI Agent giúp bạn kết nối trực tiếp với hiring manager:
-https://uctalent.io/referral/BirthdayN/yVVs9S3K-94JyZtoYOUuC?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/yVVs9S3K-94JyZtoYOUuC?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="U17" s="5" t="inlineStr">
@@ -3120,19 +3118,19 @@
       <c r="R23" s="7" t="inlineStr">
         <is>
           <t>Apply directly via our AI Agent — no middlemen, no ghosting:
-https://uctalent.io/referral/BirthdayN/FdK1xUD3EPnFBHpYxokX6?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/FdK1xUD3EPnFBHpYxokX6?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
           <t>Apply directly via our AI Agent:
-https://uctalent.io/referral/BirthdayN/FdK1xUD3EPnFBHpYxokX6?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/FdK1xUD3EPnFBHpYxokX6?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="T23" s="7" t="inlineStr">
         <is>
           <t>Apply ngay để AI Agent giúp bạn kết nối trực tiếp với hiring manager:
-https://uctalent.io/referral/BirthdayN/FdK1xUD3EPnFBHpYxokX6?utmsource=headhunter&amp;utmmedium=referral</t>
+https://uctalent.io/referral/BirthdayN/FdK1xUD3EPnFBHpYxokX6?utm_source=headhunter&amp;utm_medium=referral</t>
         </is>
       </c>
       <c r="U23" s="7" t="inlineStr">

--- a/uctalent_jobs.xlsx
+++ b/uctalent_jobs.xlsx
@@ -1074,45 +1074,40 @@
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>Hi [FirstName],
-Data QA ENGINEER — based in Vietnam (₫30,000,000-₫40,000,000/monthly). Your skills (QAQC, Corporate Services, Azure) fit.
-Open to a quick chat?
-Nhat - UCTalent</t>
+          <t>Hey! Just locked eyes with a Data QA role on Azure &amp; Databricks paying up to 40M that screams your name. 🔥 Positions like this move FAST. Let's get your CV in front of the hiring manager before someone else snaps it up. UCTalent's AI has you covered. Let's talk! Cheers</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>Most QA Engineers are just glorified manual testers waiting for a bug to pop up. If you're tired of mindless clicking and want to actually own the integrity of a massive data pipeline, listen up.
-The market is flooded with "QA experts" who can't tell a table from a spreadsheet. We don't need that. We need a Data QA Engineer who knows that data integrity is the backbone of any serious business.
-My client in Vietnam is looking for someone who doesn't just "test"—they engineer quality.
-The Reality:
-- You’ll be deep in Azure and Databricks, ensuring the Data Warehouse doesn't turn into a data swamp.
-- This is Corporate Services on a high level. Accuracy isn't a "nice to have"; it’s the only thing that matters.
-- Forget basic UI testing. We need high-level QAQC skills that actually impact the bottom line.
-Why bother?
-- Stop wasting your talent on basic web apps.
-- Work with a stack that actually challenges your brain.
-- Fast-paced, no-BS environment.
-I’ve been ghosted before, and I know it sucks. That’s why I do things differently at UCTalent. You apply, you get an answer. Simple.
-If you’re a pro and tired of the noise, let’s move. ⚡
-Link in comments 👇
-#UCTalent #DataEngineering #QAQC #VietnamJobs</t>
+          <t>Data QA Engineer.
+📍 Vietnam
+Requirements:
+- QAQC
+- Azure
+- Databricks
+- Data Warehouse
+- Corporate Services experience
+Link in comments.
+#UCTalent</t>
         </is>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>Most Data Engineers ship garbage. Stop pretending "good enough" works. 🔥
-Need a Data QA in VN who actually cares about precision. Azure + Databricks + DWH. Stop playing safe and start breaking things. ⚡
-Link in comments 👇
-#UCTalent #DataQA</t>
+          <t>Data QA Engineer 🇻🇳
+Skills: QAQC, Azure, Databricks, Data Warehouse.
+Corporate Services project.
+Link in comments.
+#UCTalent</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>Most "Data-driven" companies are flying blind because their pipelines are trash. 🗑️
-Stop letting bad data ruin decisions. If you’re a Data QA pro who breathes Azure and Databricks, I have a client in VN who actually values your brain. No more ghosting, just real impact.
-Link in comments 👇
-#UCTalent #DataEngineering</t>
+          <t>Data QA Engineer
+📍 Vietnam
+• Stack: Azure, Databricks, Data Warehouse
+• Focus: QAQC, Corporate Services
+Link in comments.
+#UCTalent</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
@@ -1129,19 +1124,19 @@
       <c r="R5" s="7" t="inlineStr">
         <is>
           <t>Apply directly via our AI Agent:
-https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utm_source=headhunter&amp;utm_medium=referral</t>
+https://uctalent.io/referral/quick_process/BN84zMIfAiuLk1OvpDqnr?utm_source=copy_link&amp;utm_medium=job_referral&amp;utm_campaign=job_referral&amp;utm_content=recruiter</t>
         </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>Apply directly:
-https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utm_source=headhunter&amp;utm_medium=referral</t>
+          <t>Apply directly via our AI Agent:
+https://uctalent.io/referral/quick_process/BN84zMIfAiuLk1OvpDqnr?utm_source=copy_link&amp;utm_medium=job_referral&amp;utm_campaign=job_referral&amp;utm_content=recruiter</t>
         </is>
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
           <t>Apply ngay:
-https://uctalent.io/referral/BirthdayN/kacSYQDAYSzM3-lkJJCxi?utm_source=headhunter&amp;utm_medium=referral</t>
+https://uctalent.io/referral/quick_process/BN84zMIfAiuLk1OvpDqnr?utm_source=copy_link&amp;utm_medium=job_referral&amp;utm_campaign=job_referral&amp;utm_content=recruiter</t>
         </is>
       </c>
       <c r="U5" s="7" t="inlineStr">
@@ -1156,7 +1151,7 @@
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t>ready_to_connect</t>
+          <t>searching</t>
         </is>
       </c>
       <c r="X5" s="6" t="inlineStr">
